--- a/cert-data/FY26-Healthcare-Certification-Courses_2026-05.xlsx
+++ b/cert-data/FY26-Healthcare-Certification-Courses_2026-05.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30219"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://konicaminoltanam-my.sharepoint.com/personal/rnesimi_kmbsus_com/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="133" documentId="8_{7392705F-DE5D-49B7-BECE-0C4C0AA9C52F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{600B5E48-5B60-45DE-817C-87CA2A96E7C8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7BC2894-4958-4898-8340-CF018B02CEB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DC5E560D-579C-485D-825F-94F306B9108B}"/>
+    <workbookView xWindow="-28920" yWindow="-11790" windowWidth="29040" windowHeight="15720" xr2:uid="{DC5E560D-579C-485D-825F-94F306B9108B}"/>
   </bookViews>
   <sheets>
     <sheet name="Healthcare Dashboard Report" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -39,6 +41,9 @@
     <t>User</t>
   </si>
   <si>
+    <t>Active Users</t>
+  </si>
+  <si>
     <t>First Name</t>
   </si>
   <si>
@@ -90,15 +95,177 @@
     <t>Curriculum Title</t>
   </si>
   <si>
-    <t>Curriculum Complete</t>
+    <t>Healthcare Curriculum Status</t>
   </si>
   <si>
     <t>Curriculum Assignment Date</t>
   </si>
   <si>
+    <t>Healthcare Certification Date</t>
+  </si>
+  <si>
+    <t>HC Qtr Certified</t>
+  </si>
+  <si>
+    <t>HC Certified</t>
+  </si>
+  <si>
+    <t>Acute Care Certification Date</t>
+  </si>
+  <si>
+    <t>Acute Care Qrt Certified</t>
+  </si>
+  <si>
+    <t>Acute Care Certified</t>
+  </si>
+  <si>
+    <t>Ambulatory Certification Date</t>
+  </si>
+  <si>
+    <t>Ambulatory Qtr Certified</t>
+  </si>
+  <si>
+    <t>Ambulatory Certified</t>
+  </si>
+  <si>
+    <t>Extended Care Certified Date</t>
+  </si>
+  <si>
+    <t>Extended Care Qtr Certified</t>
+  </si>
+  <si>
+    <t>Extended Care Certified</t>
+  </si>
+  <si>
     <t>Yes</t>
   </si>
   <si>
+    <t>Gerri</t>
+  </si>
+  <si>
+    <t>Major</t>
+  </si>
+  <si>
+    <t>Gerri.Hadley@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Major Account Executive - HS</t>
+  </si>
+  <si>
+    <t>FY2026 Direct Sales</t>
+  </si>
+  <si>
+    <t>Central Sls</t>
+  </si>
+  <si>
+    <t>Daniel</t>
+  </si>
+  <si>
+    <t>Eldridge</t>
+  </si>
+  <si>
+    <t>Daniel.Eldridge@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Sales Manager</t>
+  </si>
+  <si>
+    <t>SF</t>
+  </si>
+  <si>
+    <t>EMP_BUS</t>
+  </si>
+  <si>
+    <t>HC_CERT_FOUNDATIONS</t>
+  </si>
+  <si>
+    <t>Healthcare Certification for Direct Sales</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Philip</t>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>PWhite@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Senior Account Executive - HS</t>
+  </si>
+  <si>
+    <t>Jason</t>
+  </si>
+  <si>
+    <t>Keene</t>
+  </si>
+  <si>
+    <t>JKeene@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Shayla</t>
+  </si>
+  <si>
+    <t>Metz</t>
+  </si>
+  <si>
+    <t>SMetz@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Robert</t>
+  </si>
+  <si>
+    <t>Venturella</t>
+  </si>
+  <si>
+    <t>RVenturella@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Major Acct Sales Manager</t>
+  </si>
+  <si>
+    <t>Anna</t>
+  </si>
+  <si>
+    <t>Harbort</t>
+  </si>
+  <si>
+    <t>aharbort@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Named Account Executive - HS</t>
+  </si>
+  <si>
+    <t>West</t>
+  </si>
+  <si>
+    <t>Dapack</t>
+  </si>
+  <si>
+    <t>Phoenix</t>
+  </si>
+  <si>
+    <t>Clayton</t>
+  </si>
+  <si>
+    <t>Crane</t>
+  </si>
+  <si>
+    <t>ecrane@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Dir, Strategic Sales</t>
+  </si>
+  <si>
+    <t>Chavarria</t>
+  </si>
+  <si>
+    <t>DChavarria@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
     <t>Alexis</t>
   </si>
   <si>
@@ -108,9 +275,6 @@
     <t>AHollie@kmbs.konicaminolta.us</t>
   </si>
   <si>
-    <t>Named Account Executive - HS</t>
-  </si>
-  <si>
     <t>East</t>
   </si>
   <si>
@@ -129,16 +293,235 @@
     <t>jwalters@kmbs.konicaminolta.us</t>
   </si>
   <si>
-    <t>Sales Manager</t>
-  </si>
-  <si>
-    <t>SF</t>
-  </si>
-  <si>
-    <t>EMP_BUS</t>
-  </si>
-  <si>
-    <t>No</t>
+    <t>Susan</t>
+  </si>
+  <si>
+    <t>Bindas</t>
+  </si>
+  <si>
+    <t>SBindas@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Senior Account Executive - GES</t>
+  </si>
+  <si>
+    <t>Boca Raton</t>
+  </si>
+  <si>
+    <t>Wesley</t>
+  </si>
+  <si>
+    <t>Hardin</t>
+  </si>
+  <si>
+    <t>WHardin@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Gina</t>
+  </si>
+  <si>
+    <t>Vertullo</t>
+  </si>
+  <si>
+    <t>GVertullo@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Great Lakes</t>
+  </si>
+  <si>
+    <t>Pittsburgh</t>
+  </si>
+  <si>
+    <t>Bryan</t>
+  </si>
+  <si>
+    <t>Davis</t>
+  </si>
+  <si>
+    <t>bryan.davis@KMBS.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Mark</t>
+  </si>
+  <si>
+    <t>Brown</t>
+  </si>
+  <si>
+    <t>Mark.Brown@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Cincinnati</t>
+  </si>
+  <si>
+    <t>Michael</t>
+  </si>
+  <si>
+    <t>Mattson</t>
+  </si>
+  <si>
+    <t>MMattson@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Area VP Sales - Central</t>
+  </si>
+  <si>
+    <t>Tyler</t>
+  </si>
+  <si>
+    <t>Watling</t>
+  </si>
+  <si>
+    <t>TWatling@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Columbus</t>
+  </si>
+  <si>
+    <t>Jack</t>
+  </si>
+  <si>
+    <t>Sammons</t>
+  </si>
+  <si>
+    <t>JSammons@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Heartland Sls</t>
+  </si>
+  <si>
+    <t>Ryan</t>
+  </si>
+  <si>
+    <t>Hamilton</t>
+  </si>
+  <si>
+    <t>RHamilton@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Sean</t>
+  </si>
+  <si>
+    <t>Marshall</t>
+  </si>
+  <si>
+    <t>Smarshall@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Michelle</t>
+  </si>
+  <si>
+    <t>Ashby</t>
+  </si>
+  <si>
+    <t>MAshby@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Sr. Sales Manager</t>
+  </si>
+  <si>
+    <t>Cory</t>
+  </si>
+  <si>
+    <t>Coleman</t>
+  </si>
+  <si>
+    <t>ccoleman@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Mid-Atlantic</t>
+  </si>
+  <si>
+    <t>Nj North</t>
+  </si>
+  <si>
+    <t>Kenneth</t>
+  </si>
+  <si>
+    <t>Scheuer</t>
+  </si>
+  <si>
+    <t>KScheuer@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Dillon</t>
+  </si>
+  <si>
+    <t>Basnight</t>
+  </si>
+  <si>
+    <t>DBasnight@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Norfolk</t>
+  </si>
+  <si>
+    <t>Brian</t>
+  </si>
+  <si>
+    <t>Bullock</t>
+  </si>
+  <si>
+    <t>BBullock@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Erik</t>
+  </si>
+  <si>
+    <t>Goetzke</t>
+  </si>
+  <si>
+    <t>egoetzke@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Matthew</t>
+  </si>
+  <si>
+    <t>Doan</t>
+  </si>
+  <si>
+    <t>mdoan@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Baltimore</t>
+  </si>
+  <si>
+    <t>Sandeep</t>
+  </si>
+  <si>
+    <t>Satija</t>
+  </si>
+  <si>
+    <t>SSatija@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>North Virginia</t>
+  </si>
+  <si>
+    <t>Hur</t>
+  </si>
+  <si>
+    <t>SHur@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Philadelphia</t>
+  </si>
+  <si>
+    <t>Stephen</t>
+  </si>
+  <si>
+    <t>Farrell</t>
+  </si>
+  <si>
+    <t>SFarrell@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Terrance</t>
+  </si>
+  <si>
+    <t>O'Leary</t>
+  </si>
+  <si>
+    <t>toleary@kmbs.konicaminolta.us</t>
   </si>
   <si>
     <t>Andrea</t>
@@ -150,9 +533,6 @@
     <t>AAdkins@kmbs.konicaminolta.us</t>
   </si>
   <si>
-    <t>Major Account Executive - HS</t>
-  </si>
-  <si>
     <t>Mid-South</t>
   </si>
   <si>
@@ -168,51 +548,192 @@
     <t>Karie.Lee@kmbs.konicaminolta.us</t>
   </si>
   <si>
-    <t>Sr. Sales Manager</t>
-  </si>
-  <si>
-    <t>Anna</t>
-  </si>
-  <si>
-    <t>Harbort</t>
-  </si>
-  <si>
-    <t>aharbort@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>West</t>
-  </si>
-  <si>
-    <t>Dapack</t>
-  </si>
-  <si>
-    <t>Phoenix</t>
-  </si>
-  <si>
-    <t>Clayton</t>
-  </si>
-  <si>
-    <t>Crane</t>
-  </si>
-  <si>
-    <t>ecrane@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Dir, Strategic Sales</t>
+    <t>Dee</t>
+  </si>
+  <si>
+    <t>Gilbert</t>
+  </si>
+  <si>
+    <t>DGilbert@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Knoxville</t>
+  </si>
+  <si>
+    <t>Heather</t>
+  </si>
+  <si>
+    <t>Yeager</t>
+  </si>
+  <si>
+    <t>HYeager@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Atlanta</t>
+  </si>
+  <si>
+    <t>Leigh</t>
+  </si>
+  <si>
+    <t>Whitaker</t>
+  </si>
+  <si>
+    <t>TWhitaker@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Mid South</t>
+  </si>
+  <si>
+    <t>Caldarera</t>
+  </si>
+  <si>
+    <t>caldarer@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>New Orleans</t>
+  </si>
+  <si>
+    <t>Charles</t>
+  </si>
+  <si>
+    <t>Wollfarth</t>
+  </si>
+  <si>
+    <t>BWollfarth@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Donald</t>
+  </si>
+  <si>
+    <t>Dempsey</t>
+  </si>
+  <si>
+    <t>DDempsey@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Northeast Sls</t>
+  </si>
+  <si>
+    <t>Roger</t>
+  </si>
+  <si>
+    <t>DiGregorio</t>
+  </si>
+  <si>
+    <t>RDigregorio@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Francis</t>
+  </si>
+  <si>
+    <t>McBride</t>
+  </si>
+  <si>
+    <t>fmcbride@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Maloney</t>
+  </si>
+  <si>
+    <t>bmaloney@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Dominic</t>
+  </si>
+  <si>
+    <t>Donato</t>
+  </si>
+  <si>
+    <t>ddonato@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Texas</t>
+  </si>
+  <si>
+    <t>Dallas</t>
+  </si>
+  <si>
+    <t>Emmanuel</t>
+  </si>
+  <si>
+    <t>Torres</t>
+  </si>
+  <si>
+    <t>ETorres@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Isabella</t>
+  </si>
+  <si>
+    <t>Delgado</t>
+  </si>
+  <si>
+    <t>IDelgado@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Richard</t>
+  </si>
+  <si>
+    <t>Bortner</t>
+  </si>
+  <si>
+    <t>RBortner@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Jerry</t>
+  </si>
+  <si>
+    <t>Jelinek</t>
+  </si>
+  <si>
+    <t>JJelinek@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>San Antonio</t>
+  </si>
+  <si>
+    <t>Abigail</t>
+  </si>
+  <si>
+    <t>Adams</t>
+  </si>
+  <si>
+    <t>AAdams@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Olivia</t>
+  </si>
+  <si>
+    <t>Gilmore</t>
+  </si>
+  <si>
+    <t>ogilmore@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Ty</t>
+  </si>
+  <si>
+    <t>Foster</t>
+  </si>
+  <si>
+    <t>Ty.Foster@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Whitney</t>
+  </si>
+  <si>
+    <t>Hicks</t>
+  </si>
+  <si>
+    <t>WHicks@kmbs.konicaminolta.us</t>
   </si>
   <si>
     <t>Anne</t>
   </si>
   <si>
-    <t>Davis</t>
-  </si>
-  <si>
     <t>ADavis@kmbs.konicaminolta.us</t>
   </si>
   <si>
-    <t>FY2026 Direct Sales</t>
-  </si>
-  <si>
     <t>West Sls</t>
   </si>
   <si>
@@ -225,51 +746,12 @@
     <t>bslater@kmbs.konicaminolta.us</t>
   </si>
   <si>
-    <t>Brian</t>
-  </si>
-  <si>
     <t>Steen</t>
   </si>
   <si>
     <t>BSteen@kmbs.konicaminolta.us</t>
   </si>
   <si>
-    <t>Cory</t>
-  </si>
-  <si>
-    <t>Coleman</t>
-  </si>
-  <si>
-    <t>ccoleman@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Senior Account Executive - HS</t>
-  </si>
-  <si>
-    <t>Mid-Atlantic</t>
-  </si>
-  <si>
-    <t>Nj North</t>
-  </si>
-  <si>
-    <t>Kenneth</t>
-  </si>
-  <si>
-    <t>Scheuer</t>
-  </si>
-  <si>
-    <t>KScheuer@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Daniel</t>
-  </si>
-  <si>
-    <t>Chavarria</t>
-  </si>
-  <si>
-    <t>DChavarria@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
     <t>Danielle</t>
   </si>
   <si>
@@ -279,195 +761,6 @@
     <t>DMasella@kmbs.konicaminolta.us</t>
   </si>
   <si>
-    <t>Dee</t>
-  </si>
-  <si>
-    <t>Gilbert</t>
-  </si>
-  <si>
-    <t>DGilbert@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Knoxville</t>
-  </si>
-  <si>
-    <t>Dillon</t>
-  </si>
-  <si>
-    <t>Basnight</t>
-  </si>
-  <si>
-    <t>DBasnight@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Norfolk</t>
-  </si>
-  <si>
-    <t>Bullock</t>
-  </si>
-  <si>
-    <t>BBullock@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Dominic</t>
-  </si>
-  <si>
-    <t>Donato</t>
-  </si>
-  <si>
-    <t>ddonato@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Texas</t>
-  </si>
-  <si>
-    <t>Dallas</t>
-  </si>
-  <si>
-    <t>Emmanuel</t>
-  </si>
-  <si>
-    <t>Torres</t>
-  </si>
-  <si>
-    <t>ETorres@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Donald</t>
-  </si>
-  <si>
-    <t>Dempsey</t>
-  </si>
-  <si>
-    <t>DDempsey@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Northeast Sls</t>
-  </si>
-  <si>
-    <t>Roger</t>
-  </si>
-  <si>
-    <t>DiGregorio</t>
-  </si>
-  <si>
-    <t>RDigregorio@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Erik</t>
-  </si>
-  <si>
-    <t>Goetzke</t>
-  </si>
-  <si>
-    <t>egoetzke@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Francis</t>
-  </si>
-  <si>
-    <t>McBride</t>
-  </si>
-  <si>
-    <t>fmcbride@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Gerri</t>
-  </si>
-  <si>
-    <t>Major</t>
-  </si>
-  <si>
-    <t>Gerri.Hadley@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Central Sls</t>
-  </si>
-  <si>
-    <t>Eldridge</t>
-  </si>
-  <si>
-    <t>Daniel.Eldridge@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Gina</t>
-  </si>
-  <si>
-    <t>Vertullo</t>
-  </si>
-  <si>
-    <t>GVertullo@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Great Lakes</t>
-  </si>
-  <si>
-    <t>Pittsburgh</t>
-  </si>
-  <si>
-    <t>Bryan</t>
-  </si>
-  <si>
-    <t>bryan.davis@KMBS.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Major Acct Sales Manager</t>
-  </si>
-  <si>
-    <t>Heather</t>
-  </si>
-  <si>
-    <t>Yeager</t>
-  </si>
-  <si>
-    <t>HYeager@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Atlanta</t>
-  </si>
-  <si>
-    <t>Isabella</t>
-  </si>
-  <si>
-    <t>Delgado</t>
-  </si>
-  <si>
-    <t>IDelgado@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Richard</t>
-  </si>
-  <si>
-    <t>Bortner</t>
-  </si>
-  <si>
-    <t>RBortner@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Jack</t>
-  </si>
-  <si>
-    <t>Sammons</t>
-  </si>
-  <si>
-    <t>JSammons@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Heartland Sls</t>
-  </si>
-  <si>
-    <t>Michael</t>
-  </si>
-  <si>
-    <t>Mattson</t>
-  </si>
-  <si>
-    <t>MMattson@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Area VP Sales - Central</t>
-  </si>
-  <si>
     <t>Jeremy</t>
   </si>
   <si>
@@ -486,27 +779,6 @@
     <t>BRamos@kmbs.konicaminolta.us</t>
   </si>
   <si>
-    <t>Jerry</t>
-  </si>
-  <si>
-    <t>Jelinek</t>
-  </si>
-  <si>
-    <t>JJelinek@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>San Antonio</t>
-  </si>
-  <si>
-    <t>Abigail</t>
-  </si>
-  <si>
-    <t>Adams</t>
-  </si>
-  <si>
-    <t>AAdams@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
     <t>Kevin</t>
   </si>
   <si>
@@ -523,276 +795,6 @@
   </si>
   <si>
     <t>JIbon@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Leigh</t>
-  </si>
-  <si>
-    <t>Whitaker</t>
-  </si>
-  <si>
-    <t>TWhitaker@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Mid South</t>
-  </si>
-  <si>
-    <t>Mark</t>
-  </si>
-  <si>
-    <t>Brown</t>
-  </si>
-  <si>
-    <t>Mark.Brown@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Cincinnati</t>
-  </si>
-  <si>
-    <t>Caldarera</t>
-  </si>
-  <si>
-    <t>caldarer@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>New Orleans</t>
-  </si>
-  <si>
-    <t>Charles</t>
-  </si>
-  <si>
-    <t>Wollfarth</t>
-  </si>
-  <si>
-    <t>BWollfarth@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Matthew</t>
-  </si>
-  <si>
-    <t>Doan</t>
-  </si>
-  <si>
-    <t>mdoan@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Baltimore</t>
-  </si>
-  <si>
-    <t>Olivia</t>
-  </si>
-  <si>
-    <t>Gilmore</t>
-  </si>
-  <si>
-    <t>ogilmore@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Philip</t>
-  </si>
-  <si>
-    <t>White</t>
-  </si>
-  <si>
-    <t>PWhite@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Jason</t>
-  </si>
-  <si>
-    <t>Keene</t>
-  </si>
-  <si>
-    <t>JKeene@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Robert</t>
-  </si>
-  <si>
-    <t>Maloney</t>
-  </si>
-  <si>
-    <t>bmaloney@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Ryan</t>
-  </si>
-  <si>
-    <t>Hamilton</t>
-  </si>
-  <si>
-    <t>RHamilton@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Sandeep</t>
-  </si>
-  <si>
-    <t>Satija</t>
-  </si>
-  <si>
-    <t>SSatija@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>North Virginia</t>
-  </si>
-  <si>
-    <t>Sean</t>
-  </si>
-  <si>
-    <t>Hur</t>
-  </si>
-  <si>
-    <t>SHur@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Philadelphia</t>
-  </si>
-  <si>
-    <t>Marshall</t>
-  </si>
-  <si>
-    <t>Smarshall@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Michelle</t>
-  </si>
-  <si>
-    <t>Ashby</t>
-  </si>
-  <si>
-    <t>MAshby@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Shayla</t>
-  </si>
-  <si>
-    <t>Metz</t>
-  </si>
-  <si>
-    <t>SMetz@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Venturella</t>
-  </si>
-  <si>
-    <t>RVenturella@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Stephen</t>
-  </si>
-  <si>
-    <t>Farrell</t>
-  </si>
-  <si>
-    <t>SFarrell@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Susan</t>
-  </si>
-  <si>
-    <t>Bindas</t>
-  </si>
-  <si>
-    <t>SBindas@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Senior Account Executive - GES</t>
-  </si>
-  <si>
-    <t>Boca Raton</t>
-  </si>
-  <si>
-    <t>Wesley</t>
-  </si>
-  <si>
-    <t>Hardin</t>
-  </si>
-  <si>
-    <t>WHardin@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Terrance</t>
-  </si>
-  <si>
-    <t>O'Leary</t>
-  </si>
-  <si>
-    <t>toleary@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Ty</t>
-  </si>
-  <si>
-    <t>Foster</t>
-  </si>
-  <si>
-    <t>Ty.Foster@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Tyler</t>
-  </si>
-  <si>
-    <t>Watling</t>
-  </si>
-  <si>
-    <t>TWatling@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Columbus</t>
-  </si>
-  <si>
-    <t>Whitney</t>
-  </si>
-  <si>
-    <t>Hicks</t>
-  </si>
-  <si>
-    <t>WHicks@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Healthcare Certification Date</t>
-  </si>
-  <si>
-    <t>HC Certified</t>
-  </si>
-  <si>
-    <t>HC Qtr Certified</t>
-  </si>
-  <si>
-    <t>Ambulatory Certified</t>
-  </si>
-  <si>
-    <t>Extended Care Certified</t>
-  </si>
-  <si>
-    <t>Ambulatory Certification Date</t>
-  </si>
-  <si>
-    <t>Ambulatory Qtr Certified</t>
-  </si>
-  <si>
-    <t>Extended Care Certified Date</t>
-  </si>
-  <si>
-    <t>Extended Care Qtr Certified</t>
-  </si>
-  <si>
-    <t>Acute Care Certification Date</t>
-  </si>
-  <si>
-    <t>Acute Care Qrt Certified</t>
-  </si>
-  <si>
-    <t>Acute Care Certified</t>
-  </si>
-  <si>
-    <t>Active Users</t>
-  </si>
-  <si>
-    <t>HC_CERT_FOUNDATIONS</t>
-  </si>
-  <si>
-    <t>Healthcare Certification for Direct Sales</t>
   </si>
   <si>
     <t>Eric</t>
@@ -982,7 +984,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1551,7 +1553,7 @@
   </cellStyles>
   <dxfs count="15">
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1590,7 +1592,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1638,7 +1640,7 @@
   </sortState>
   <tableColumns count="33">
     <tableColumn id="1" xr3:uid="{7E27C642-CD96-4E29-8515-090A1E2597B4}" name="User"/>
-    <tableColumn id="21" xr3:uid="{50452B11-87F7-47DB-9B0B-60BC2C16FB02}" name="Active Users" dataDxfId="0"/>
+    <tableColumn id="21" xr3:uid="{50452B11-87F7-47DB-9B0B-60BC2C16FB02}" name="Active Users" dataDxfId="13"/>
     <tableColumn id="2" xr3:uid="{CFFAECCF-72C9-4975-9126-F750BD17086F}" name="First Name"/>
     <tableColumn id="3" xr3:uid="{72D560DD-C804-4CCA-A0AF-6E9765DBE97D}" name="Last Name"/>
     <tableColumn id="4" xr3:uid="{DA0EF794-C5D7-4C59-BF79-583C74C9F984}" name="Email Address"/>
@@ -1656,28 +1658,28 @@
     <tableColumn id="16" xr3:uid="{DA637367-4B1A-4718-9F40-B3224058DC7F}" name="Parent Curriculum ID"/>
     <tableColumn id="17" xr3:uid="{32EA0DBB-54BA-4A15-AD27-1BA24212FA5E}" name="Curriculum ID"/>
     <tableColumn id="18" xr3:uid="{F9F5F60C-1269-4602-89D5-FF53AB8C2F04}" name="Curriculum Title"/>
-    <tableColumn id="19" xr3:uid="{95B523F6-0B3B-467F-86F6-5135D4A96D8B}" name="Curriculum Complete" dataDxfId="13"/>
+    <tableColumn id="19" xr3:uid="{95B523F6-0B3B-467F-86F6-5135D4A96D8B}" name="Healthcare Curriculum Status" dataDxfId="12"/>
     <tableColumn id="20" xr3:uid="{7FC75486-8403-40F2-92ED-6F990AD8EB85}" name="Curriculum Assignment Date"/>
-    <tableColumn id="24" xr3:uid="{70885FE9-BF2C-444A-BEB9-54BB4010DA6A}" name="Healthcare Certification Date" dataDxfId="12"/>
-    <tableColumn id="25" xr3:uid="{5888C70D-72C2-4292-BC2A-7A15997DF1E9}" name="HC Qtr Certified" dataDxfId="11">
+    <tableColumn id="24" xr3:uid="{70885FE9-BF2C-444A-BEB9-54BB4010DA6A}" name="Healthcare Certification Date" dataDxfId="11"/>
+    <tableColumn id="25" xr3:uid="{5888C70D-72C2-4292-BC2A-7A15997DF1E9}" name="HC Qtr Certified" dataDxfId="10">
       <calculatedColumnFormula>"FY"&amp;YEAR(V2)-IF(MONTH(V2)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(V2),{1,4,7,10}),"Q4","Q1","Q2","Q3")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{5C33DCD2-2B3F-4399-8CEB-750948111A65}" name="HC Certified" dataDxfId="10"/>
-    <tableColumn id="33" xr3:uid="{89770A35-3D52-486D-AFE9-CADA18FC192F}" name="Acute Care Certification Date" dataDxfId="9"/>
-    <tableColumn id="34" xr3:uid="{D4913749-1881-474D-B3B3-0BBCA31DA1CF}" name="Acute Care Qrt Certified" dataDxfId="8">
+    <tableColumn id="26" xr3:uid="{5C33DCD2-2B3F-4399-8CEB-750948111A65}" name="HC Certified" dataDxfId="9"/>
+    <tableColumn id="33" xr3:uid="{89770A35-3D52-486D-AFE9-CADA18FC192F}" name="Acute Care Certification Date" dataDxfId="8"/>
+    <tableColumn id="34" xr3:uid="{D4913749-1881-474D-B3B3-0BBCA31DA1CF}" name="Acute Care Qrt Certified" dataDxfId="7">
       <calculatedColumnFormula>"FY"&amp;YEAR(Y2)-IF(MONTH(Y2)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y2),{1,4,7,10}),"Q4","Q1","Q2","Q3")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="35" xr3:uid="{748E363B-F498-467B-AA4F-3B39F988ACC3}" name="Acute Care Certified" dataDxfId="7"/>
-    <tableColumn id="27" xr3:uid="{42140B36-5C81-4C80-B342-0C81AE28861C}" name="Ambulatory Certification Date" dataDxfId="6"/>
-    <tableColumn id="28" xr3:uid="{439B84FE-DB2D-4723-8A20-8FD9FC959B76}" name="Ambulatory Qtr Certified" dataDxfId="5">
+    <tableColumn id="35" xr3:uid="{748E363B-F498-467B-AA4F-3B39F988ACC3}" name="Acute Care Certified" dataDxfId="6"/>
+    <tableColumn id="27" xr3:uid="{42140B36-5C81-4C80-B342-0C81AE28861C}" name="Ambulatory Certification Date" dataDxfId="5"/>
+    <tableColumn id="28" xr3:uid="{439B84FE-DB2D-4723-8A20-8FD9FC959B76}" name="Ambulatory Qtr Certified" dataDxfId="4">
       <calculatedColumnFormula>"FY"&amp;YEAR(AB2)-IF(MONTH(AB2)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(AB2),{1,4,7,10}),"Q4","Q1","Q2","Q3")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{8051C9E6-4B56-4BDE-B62E-0612113A19C1}" name="Ambulatory Certified" dataDxfId="4"/>
-    <tableColumn id="30" xr3:uid="{E87F21B3-F799-42C5-B8A3-2612ED64F64F}" name="Extended Care Certified Date" dataDxfId="3"/>
-    <tableColumn id="31" xr3:uid="{A57AA683-A269-4B5C-9F95-C1134B240CDA}" name="Extended Care Qtr Certified" dataDxfId="2">
+    <tableColumn id="29" xr3:uid="{8051C9E6-4B56-4BDE-B62E-0612113A19C1}" name="Ambulatory Certified" dataDxfId="3"/>
+    <tableColumn id="30" xr3:uid="{E87F21B3-F799-42C5-B8A3-2612ED64F64F}" name="Extended Care Certified Date" dataDxfId="2"/>
+    <tableColumn id="31" xr3:uid="{A57AA683-A269-4B5C-9F95-C1134B240CDA}" name="Extended Care Qtr Certified" dataDxfId="1">
       <calculatedColumnFormula>"FY"&amp;YEAR(AE2)-IF(MONTH(AE2)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(AE2),{1,4,7,10}),"Q4","Q1","Q2","Q3")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="32" xr3:uid="{8CB51375-2C9A-4260-B258-937D732898ED}" name="Extended Care Certified" dataDxfId="1"/>
+    <tableColumn id="32" xr3:uid="{8CB51375-2C9A-4260-B258-937D732898ED}" name="Extended Care Certified" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2001,455 +2003,438 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBB48FCD-FA24-4849-AC79-BFCF63E0FF44}">
   <dimension ref="A1:AG60"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1796875" customWidth="1"/>
-    <col min="4" max="4" width="11.90625" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" customWidth="1"/>
     <col min="5" max="5" width="33" customWidth="1"/>
-    <col min="6" max="6" width="26.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.54296875" customWidth="1"/>
-    <col min="8" max="8" width="35.26953125" customWidth="1"/>
-    <col min="9" max="9" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.5703125" customWidth="1"/>
+    <col min="8" max="8" width="35.28515625" customWidth="1"/>
+    <col min="9" max="9" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19" customWidth="1"/>
-    <col min="11" max="11" width="18.7265625" customWidth="1"/>
-    <col min="12" max="12" width="36.36328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.90625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.26953125" customWidth="1"/>
-    <col min="15" max="15" width="11.08984375" customWidth="1"/>
-    <col min="16" max="16" width="11.90625" customWidth="1"/>
-    <col min="17" max="17" width="20.90625" customWidth="1"/>
-    <col min="18" max="18" width="14.90625" customWidth="1"/>
-    <col min="19" max="19" width="21.08984375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="21.54296875" style="2" customWidth="1"/>
-    <col min="21" max="21" width="27.54296875" customWidth="1"/>
-    <col min="22" max="22" width="31.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="25.453125" style="2" customWidth="1"/>
-    <col min="24" max="24" width="13.81640625" style="2" customWidth="1"/>
-    <col min="25" max="25" width="31.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="13.81640625" style="2" customWidth="1"/>
-    <col min="28" max="28" width="29.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.7109375" customWidth="1"/>
+    <col min="12" max="12" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.28515625" customWidth="1"/>
+    <col min="15" max="15" width="11.140625" customWidth="1"/>
+    <col min="16" max="16" width="11.85546875" customWidth="1"/>
+    <col min="17" max="17" width="20.85546875" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" customWidth="1"/>
+    <col min="19" max="19" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="34.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="27.5703125" customWidth="1"/>
+    <col min="22" max="22" width="31.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="25.42578125" style="2" customWidth="1"/>
+    <col min="24" max="24" width="13.85546875" style="2" customWidth="1"/>
+    <col min="25" max="25" width="31.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="26.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="23.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="29.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="24" style="2" customWidth="1"/>
-    <col min="30" max="30" width="20.90625" style="2" customWidth="1"/>
-    <col min="31" max="31" width="31.36328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="20.85546875" style="2" customWidth="1"/>
+    <col min="31" max="31" width="31.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="30" style="2" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="26.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="26.7109375" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:33">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>238</v>
+        <v>21</v>
       </c>
       <c r="W1" s="4" t="s">
-        <v>240</v>
+        <v>22</v>
       </c>
       <c r="X1" s="6" t="s">
-        <v>239</v>
+        <v>23</v>
       </c>
       <c r="Y1" s="2" t="s">
-        <v>247</v>
+        <v>24</v>
       </c>
       <c r="Z1" s="2" t="s">
-        <v>248</v>
+        <v>25</v>
       </c>
       <c r="AA1" s="6" t="s">
-        <v>249</v>
+        <v>26</v>
       </c>
       <c r="AB1" s="2" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="AC1" s="4" t="s">
-        <v>244</v>
+        <v>28</v>
       </c>
       <c r="AD1" s="5" t="s">
-        <v>241</v>
+        <v>29</v>
       </c>
       <c r="AE1" s="4" t="s">
-        <v>245</v>
+        <v>30</v>
       </c>
       <c r="AF1" s="4" t="s">
-        <v>246</v>
+        <v>31</v>
       </c>
       <c r="AG1" s="5" t="s">
-        <v>242</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:33">
       <c r="A2">
         <v>103900</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>113</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
-        <v>114</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" t="s">
         <v>38</v>
       </c>
-      <c r="G2" t="s">
-        <v>58</v>
-      </c>
       <c r="H2" t="s">
-        <v>115</v>
+        <v>39</v>
       </c>
       <c r="I2" t="s">
-        <v>115</v>
+        <v>39</v>
       </c>
       <c r="J2" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="K2" t="s">
-        <v>116</v>
+        <v>41</v>
       </c>
       <c r="L2" t="s">
-        <v>117</v>
+        <v>42</v>
       </c>
       <c r="M2" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="N2" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O2" s="1">
         <v>39601</v>
       </c>
       <c r="P2" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q2" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R2" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S2" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U2" s="1">
         <v>44343</v>
       </c>
       <c r="X2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y2" s="7">
-        <v>46238</v>
-      </c>
-      <c r="Z2" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y2)-IF(MONTH(Y2)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y2),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Y2" s="7"/>
       <c r="AA2" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AD2" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG2" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:33">
       <c r="A3">
         <v>103906</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s">
-        <v>184</v>
+        <v>49</v>
       </c>
       <c r="D3" t="s">
-        <v>185</v>
+        <v>50</v>
       </c>
       <c r="E3" t="s">
-        <v>186</v>
+        <v>51</v>
       </c>
       <c r="F3" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="G3" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="H3" t="s">
-        <v>115</v>
+        <v>39</v>
       </c>
       <c r="I3" t="s">
-        <v>115</v>
+        <v>39</v>
       </c>
       <c r="J3" t="s">
-        <v>187</v>
+        <v>53</v>
       </c>
       <c r="K3" t="s">
-        <v>188</v>
+        <v>54</v>
       </c>
       <c r="L3" t="s">
-        <v>189</v>
+        <v>55</v>
       </c>
       <c r="M3" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="N3" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O3" s="1">
         <v>38808</v>
       </c>
       <c r="P3" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q3" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R3" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S3" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U3" s="1">
         <v>44343</v>
       </c>
       <c r="X3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y3" s="7">
-        <v>46251</v>
-      </c>
-      <c r="Z3" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y3)-IF(MONTH(Y3)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y3),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Y3" s="7"/>
       <c r="AA3" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AD3" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG3" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:33">
       <c r="A4">
         <v>123862</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>209</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s">
-        <v>210</v>
+        <v>57</v>
       </c>
       <c r="E4" t="s">
-        <v>211</v>
+        <v>58</v>
       </c>
       <c r="F4" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="G4" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="H4" t="s">
-        <v>115</v>
+        <v>39</v>
       </c>
       <c r="I4" t="s">
-        <v>115</v>
+        <v>39</v>
       </c>
       <c r="J4" t="s">
-        <v>190</v>
+        <v>59</v>
       </c>
       <c r="K4" t="s">
-        <v>212</v>
+        <v>60</v>
       </c>
       <c r="L4" t="s">
-        <v>213</v>
+        <v>61</v>
       </c>
       <c r="M4" t="s">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="N4" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O4" s="1">
         <v>45706</v>
       </c>
       <c r="P4" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q4" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R4" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S4" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U4" s="1">
         <v>45706</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y4" s="7">
-        <v>46257</v>
-      </c>
-      <c r="Z4" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y4)-IF(MONTH(Y4)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y4),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Y4" s="7"/>
       <c r="AA4" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AD4" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG4" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:33">
       <c r="A5">
         <v>127835</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="E5" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G5" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="H5" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="I5" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="J5" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="K5" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="L5" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="M5" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="N5" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O5" s="1">
         <v>45488</v>
       </c>
       <c r="P5" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q5" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R5" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S5" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U5" s="1">
         <v>45488</v>
@@ -2462,169 +2447,157 @@
         <v>FY2025 Q4</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y5" s="7">
-        <v>46226</v>
-      </c>
-      <c r="Z5" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y5)-IF(MONTH(Y5)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y5),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="Y5" s="7"/>
       <c r="AA5" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AD5" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG5" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:33">
       <c r="A6">
         <v>128348</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E6" t="s">
         <v>75</v>
       </c>
-      <c r="D6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E6" t="s">
-        <v>77</v>
-      </c>
       <c r="F6" t="s">
+        <v>52</v>
+      </c>
+      <c r="G6" t="s">
+        <v>67</v>
+      </c>
+      <c r="H6" t="s">
+        <v>68</v>
+      </c>
+      <c r="I6" t="s">
         <v>69</v>
       </c>
-      <c r="G6" t="s">
-        <v>48</v>
-      </c>
-      <c r="H6" t="s">
-        <v>49</v>
-      </c>
-      <c r="I6" t="s">
-        <v>50</v>
-      </c>
       <c r="J6" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="K6" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="L6" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="M6" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="N6" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O6" s="1">
         <v>45642</v>
       </c>
       <c r="P6" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q6" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R6" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S6" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U6" s="1">
         <v>45642</v>
       </c>
       <c r="X6" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y6" s="7">
-        <v>46230</v>
-      </c>
-      <c r="Z6" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y6)-IF(MONTH(Y6)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y6),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Y6" s="7"/>
       <c r="AA6" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AD6" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG6" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:33">
       <c r="A7">
         <v>128947</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="F7" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G7" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="H7" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="I7" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="J7" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="K7" t="s">
-        <v>29</v>
+        <v>83</v>
       </c>
       <c r="L7" t="s">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="M7" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="N7" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O7" s="1">
         <v>45915</v>
       </c>
       <c r="P7" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q7" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R7" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S7" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U7" s="1">
         <v>45916</v>
@@ -2637,1359 +2610,1251 @@
         <v>FY2026 Q1</v>
       </c>
       <c r="X7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y7" s="7">
-        <v>46224</v>
-      </c>
-      <c r="Z7" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y7)-IF(MONTH(Y7)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y7),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="Y7" s="7"/>
       <c r="AA7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB7" s="7">
-        <v>46224</v>
-      </c>
-      <c r="AC7" s="2" t="str">
-        <f>"FY"&amp;YEAR(AB7)-IF(MONTH(AB7)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(AB7),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="AB7" s="7"/>
       <c r="AD7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="AE7" s="7">
-        <v>46224</v>
-      </c>
-      <c r="AF7" s="2" t="str">
-        <f>"FY"&amp;YEAR(AE7)-IF(MONTH(AE7)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(AE7),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="AE7" s="7"/>
       <c r="AG7" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:33">
       <c r="A8">
         <v>122904</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>217</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>218</v>
+        <v>86</v>
       </c>
       <c r="E8" t="s">
-        <v>219</v>
+        <v>87</v>
       </c>
       <c r="F8" t="s">
-        <v>220</v>
+        <v>88</v>
       </c>
       <c r="G8" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="H8" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="I8" t="s">
-        <v>221</v>
+        <v>89</v>
       </c>
       <c r="J8" t="s">
-        <v>222</v>
+        <v>90</v>
       </c>
       <c r="K8" t="s">
-        <v>223</v>
+        <v>91</v>
       </c>
       <c r="L8" t="s">
-        <v>224</v>
+        <v>92</v>
       </c>
       <c r="M8" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="N8" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O8" s="1">
         <v>43591</v>
       </c>
       <c r="P8" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q8" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R8" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S8" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U8" s="1">
         <v>44343</v>
       </c>
       <c r="X8" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y8" s="7">
-        <v>46259</v>
-      </c>
-      <c r="Z8" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y8)-IF(MONTH(Y8)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y8),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Y8" s="7"/>
       <c r="AA8" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AD8" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG8" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:33">
       <c r="A9">
         <v>129182</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="F9" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G9" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="H9" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="I9" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="J9" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="K9" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="L9" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="M9" t="s">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="N9" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O9" s="1">
         <v>45999</v>
       </c>
       <c r="P9" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q9" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R9" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S9" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U9" s="1">
         <v>46000</v>
       </c>
       <c r="X9" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y9" s="7">
-        <v>46239</v>
-      </c>
-      <c r="Z9" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y9)-IF(MONTH(Y9)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y9),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Y9" s="7"/>
       <c r="AA9" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AD9" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG9" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:33">
       <c r="A10">
         <v>115144</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>167</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>168</v>
+        <v>102</v>
       </c>
       <c r="E10" t="s">
-        <v>169</v>
+        <v>103</v>
       </c>
       <c r="F10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G10" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="H10" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="I10" t="s">
-        <v>170</v>
+        <v>104</v>
       </c>
       <c r="J10" t="s">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="K10" t="s">
-        <v>141</v>
+        <v>106</v>
       </c>
       <c r="L10" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="M10" t="s">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="N10" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O10" s="1">
         <v>41362</v>
       </c>
       <c r="P10" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q10" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R10" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S10" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U10" s="1">
         <v>44340</v>
       </c>
       <c r="X10" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y10" s="7">
-        <v>46247</v>
-      </c>
-      <c r="Z10" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y10)-IF(MONTH(Y10)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y10),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Y10" s="7"/>
       <c r="AA10" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AD10" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG10" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:33">
       <c r="A11">
         <v>125310</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>231</v>
+        <v>109</v>
       </c>
       <c r="D11" t="s">
-        <v>232</v>
+        <v>110</v>
       </c>
       <c r="E11" t="s">
-        <v>233</v>
+        <v>111</v>
       </c>
       <c r="F11" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="G11" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="H11" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="I11" t="s">
-        <v>234</v>
+        <v>112</v>
       </c>
       <c r="J11" t="s">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="K11" t="s">
-        <v>141</v>
+        <v>106</v>
       </c>
       <c r="L11" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="M11" t="s">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="N11" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O11" s="1">
         <v>44627</v>
       </c>
       <c r="P11" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q11" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R11" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S11" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U11" s="1">
         <v>44636</v>
       </c>
       <c r="X11" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y11" s="7">
-        <v>46262</v>
-      </c>
-      <c r="Z11" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y11)-IF(MONTH(Y11)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y11),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Y11" s="7"/>
       <c r="AA11" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AD11" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG11" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:33">
       <c r="A12">
         <v>126783</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="D12" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="E12" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="F12" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G12" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="H12" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="I12" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="J12" t="s">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="K12" t="s">
-        <v>141</v>
+        <v>106</v>
       </c>
       <c r="L12" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="M12" t="s">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="N12" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O12" s="1">
         <v>45117</v>
       </c>
       <c r="P12" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q12" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R12" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S12" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U12" s="1">
         <v>45194</v>
       </c>
       <c r="X12" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y12" s="7">
-        <v>46242</v>
-      </c>
-      <c r="Z12" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y12)-IF(MONTH(Y12)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y12),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Y12" s="7"/>
       <c r="AA12" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AD12" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG12" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:33">
       <c r="A13">
         <v>120343</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>193</v>
+        <v>117</v>
       </c>
       <c r="D13" t="s">
-        <v>194</v>
+        <v>118</v>
       </c>
       <c r="E13" t="s">
-        <v>195</v>
+        <v>119</v>
       </c>
       <c r="F13" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" t="s">
         <v>38</v>
       </c>
-      <c r="G13" t="s">
-        <v>58</v>
-      </c>
       <c r="H13" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="I13" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="J13" t="s">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="K13" t="s">
-        <v>141</v>
+        <v>106</v>
       </c>
       <c r="L13" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="M13" t="s">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="N13" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O13" s="1">
         <v>42821</v>
       </c>
       <c r="P13" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q13" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R13" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S13" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U13" s="1">
         <v>44323</v>
       </c>
       <c r="X13" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y13" s="7">
-        <v>46253</v>
-      </c>
-      <c r="Z13" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y13)-IF(MONTH(Y13)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y13),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Y13" s="7"/>
       <c r="AA13" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AD13" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG13" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:33">
       <c r="A14">
         <v>117563</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="D14" t="s">
-        <v>204</v>
+        <v>121</v>
       </c>
       <c r="E14" t="s">
-        <v>205</v>
+        <v>122</v>
       </c>
       <c r="F14" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="G14" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="H14" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="I14" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="J14" t="s">
-        <v>206</v>
+        <v>123</v>
       </c>
       <c r="K14" t="s">
-        <v>207</v>
+        <v>124</v>
       </c>
       <c r="L14" t="s">
-        <v>208</v>
+        <v>125</v>
       </c>
       <c r="M14" t="s">
+        <v>126</v>
+      </c>
+      <c r="N14" t="s">
         <v>44</v>
-      </c>
-      <c r="N14" t="s">
-        <v>32</v>
       </c>
       <c r="O14" s="1">
         <v>42100</v>
       </c>
       <c r="P14" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q14" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R14" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S14" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U14" s="1">
         <v>44372</v>
       </c>
       <c r="X14" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y14" s="7">
-        <v>46256</v>
-      </c>
-      <c r="Z14" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y14)-IF(MONTH(Y14)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y14),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Y14" s="7"/>
       <c r="AA14" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AD14" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG14" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:33">
       <c r="A15">
         <v>128013</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>66</v>
+        <v>127</v>
       </c>
       <c r="D15" t="s">
-        <v>67</v>
+        <v>128</v>
       </c>
       <c r="E15" t="s">
-        <v>68</v>
+        <v>129</v>
       </c>
       <c r="F15" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="G15" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="H15" t="s">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="I15" t="s">
-        <v>71</v>
+        <v>131</v>
       </c>
       <c r="J15" t="s">
-        <v>72</v>
+        <v>132</v>
       </c>
       <c r="K15" t="s">
+        <v>133</v>
+      </c>
+      <c r="L15" t="s">
+        <v>134</v>
+      </c>
+      <c r="M15" t="s">
         <v>73</v>
       </c>
-      <c r="L15" t="s">
-        <v>74</v>
-      </c>
-      <c r="M15" t="s">
-        <v>54</v>
-      </c>
       <c r="N15" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O15" s="1">
         <v>45544</v>
       </c>
       <c r="P15" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q15" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R15" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S15" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U15" s="1">
         <v>45544</v>
       </c>
       <c r="X15" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y15" s="7">
-        <v>46229</v>
-      </c>
-      <c r="Z15" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y15)-IF(MONTH(Y15)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y15),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Y15" s="7"/>
       <c r="AA15" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AD15" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG15" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:33">
       <c r="A16">
         <v>129377</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>85</v>
+        <v>135</v>
       </c>
       <c r="D16" t="s">
-        <v>86</v>
+        <v>136</v>
       </c>
       <c r="E16" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="F16" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G16" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="H16" t="s">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="I16" t="s">
-        <v>88</v>
+        <v>138</v>
       </c>
       <c r="J16" t="s">
-        <v>63</v>
+        <v>139</v>
       </c>
       <c r="K16" t="s">
-        <v>89</v>
+        <v>140</v>
       </c>
       <c r="L16" t="s">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="M16" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="N16" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O16" s="1">
         <v>46132</v>
       </c>
       <c r="P16" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q16" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R16" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S16" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U16" s="1">
         <v>46132</v>
       </c>
       <c r="X16" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y16" s="7">
-        <v>46233</v>
-      </c>
-      <c r="Z16" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y16)-IF(MONTH(Y16)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y16),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Y16" s="7"/>
       <c r="AA16" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AD16" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG16" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:33">
       <c r="A17">
         <v>125940</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>106</v>
+        <v>142</v>
       </c>
       <c r="D17" t="s">
-        <v>107</v>
+        <v>143</v>
       </c>
       <c r="E17" t="s">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="F17" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G17" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="H17" t="s">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="I17" t="s">
-        <v>88</v>
+        <v>138</v>
       </c>
       <c r="J17" t="s">
-        <v>63</v>
+        <v>139</v>
       </c>
       <c r="K17" t="s">
-        <v>89</v>
+        <v>140</v>
       </c>
       <c r="L17" t="s">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="M17" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="N17" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O17" s="1">
         <v>44825</v>
       </c>
       <c r="P17" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q17" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R17" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S17" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U17" s="1">
         <v>45226</v>
       </c>
       <c r="X17" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y17" s="7">
-        <v>46236</v>
-      </c>
-      <c r="Z17" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y17)-IF(MONTH(Y17)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y17),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Y17" s="7"/>
       <c r="AA17" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AD17" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG17" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:33">
       <c r="A18">
         <v>127473</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C18" t="s">
-        <v>177</v>
+        <v>145</v>
       </c>
       <c r="D18" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="E18" t="s">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="F18" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G18" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="H18" t="s">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="I18" t="s">
-        <v>180</v>
+        <v>148</v>
       </c>
       <c r="J18" t="s">
-        <v>63</v>
+        <v>139</v>
       </c>
       <c r="K18" t="s">
-        <v>89</v>
+        <v>140</v>
       </c>
       <c r="L18" t="s">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="M18" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="N18" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O18" s="1">
         <v>45393</v>
       </c>
       <c r="P18" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q18" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R18" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S18" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U18" s="1">
         <v>45393</v>
       </c>
       <c r="X18" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y18" s="7">
-        <v>46249</v>
-      </c>
-      <c r="Z18" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y18)-IF(MONTH(Y18)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y18),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Y18" s="7"/>
       <c r="AA18" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AD18" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG18" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:33">
       <c r="A19">
         <v>129153</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C19" t="s">
-        <v>196</v>
+        <v>149</v>
       </c>
       <c r="D19" t="s">
-        <v>197</v>
+        <v>150</v>
       </c>
       <c r="E19" t="s">
-        <v>198</v>
+        <v>151</v>
       </c>
       <c r="F19" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G19" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="H19" t="s">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="I19" t="s">
-        <v>199</v>
+        <v>152</v>
       </c>
       <c r="J19" t="s">
-        <v>63</v>
+        <v>139</v>
       </c>
       <c r="K19" t="s">
-        <v>89</v>
+        <v>140</v>
       </c>
       <c r="L19" t="s">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="M19" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="N19" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O19" s="1">
         <v>46006</v>
       </c>
       <c r="P19" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q19" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R19" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S19" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U19" s="1">
         <v>46006</v>
       </c>
       <c r="X19" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y19" s="7">
-        <v>46254</v>
-      </c>
-      <c r="Z19" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y19)-IF(MONTH(Y19)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y19),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Y19" s="7"/>
       <c r="AA19" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AD19" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG19" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:33">
       <c r="A20">
         <v>128757</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C20" t="s">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="D20" t="s">
-        <v>201</v>
+        <v>153</v>
       </c>
       <c r="E20" t="s">
-        <v>202</v>
+        <v>154</v>
       </c>
       <c r="F20" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="G20" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="I20" t="s">
-        <v>203</v>
+        <v>155</v>
       </c>
       <c r="J20" t="s">
-        <v>72</v>
+        <v>132</v>
       </c>
       <c r="K20" t="s">
+        <v>133</v>
+      </c>
+      <c r="L20" t="s">
+        <v>134</v>
+      </c>
+      <c r="M20" t="s">
         <v>73</v>
       </c>
-      <c r="L20" t="s">
-        <v>74</v>
-      </c>
-      <c r="M20" t="s">
-        <v>54</v>
-      </c>
       <c r="N20" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O20" s="1">
         <v>45796</v>
       </c>
       <c r="P20" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q20" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R20" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S20" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U20" s="1">
         <v>45796</v>
       </c>
       <c r="X20" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y20" s="7">
-        <v>46255</v>
-      </c>
-      <c r="Z20" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y20)-IF(MONTH(Y20)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y20),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Y20" s="7"/>
       <c r="AA20" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AD20" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG20" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:33">
       <c r="A21">
         <v>128321</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C21" t="s">
-        <v>214</v>
+        <v>156</v>
       </c>
       <c r="D21" t="s">
-        <v>215</v>
+        <v>157</v>
       </c>
       <c r="E21" t="s">
-        <v>216</v>
+        <v>158</v>
       </c>
       <c r="F21" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G21" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="I21" t="s">
-        <v>71</v>
+        <v>131</v>
       </c>
       <c r="J21" t="s">
-        <v>72</v>
+        <v>132</v>
       </c>
       <c r="K21" t="s">
+        <v>133</v>
+      </c>
+      <c r="L21" t="s">
+        <v>134</v>
+      </c>
+      <c r="M21" t="s">
         <v>73</v>
       </c>
-      <c r="L21" t="s">
-        <v>74</v>
-      </c>
-      <c r="M21" t="s">
-        <v>54</v>
-      </c>
       <c r="N21" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O21" s="1">
         <v>45664</v>
       </c>
       <c r="P21" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q21" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R21" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S21" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U21" s="1">
         <v>45664</v>
       </c>
       <c r="X21" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y21" s="7">
-        <v>46258</v>
-      </c>
-      <c r="Z21" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y21)-IF(MONTH(Y21)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y21),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Y21" s="7"/>
       <c r="AA21" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AD21" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG21" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:33">
       <c r="A22">
         <v>127826</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C22" t="s">
-        <v>225</v>
+        <v>159</v>
       </c>
       <c r="D22" t="s">
-        <v>226</v>
+        <v>160</v>
       </c>
       <c r="E22" t="s">
-        <v>227</v>
+        <v>161</v>
       </c>
       <c r="F22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G22" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="H22" t="s">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="I22" t="s">
-        <v>203</v>
+        <v>155</v>
       </c>
       <c r="J22" t="s">
-        <v>72</v>
+        <v>132</v>
       </c>
       <c r="K22" t="s">
+        <v>133</v>
+      </c>
+      <c r="L22" t="s">
+        <v>134</v>
+      </c>
+      <c r="M22" t="s">
         <v>73</v>
       </c>
-      <c r="L22" t="s">
-        <v>74</v>
-      </c>
-      <c r="M22" t="s">
-        <v>54</v>
-      </c>
       <c r="N22" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O22" s="1">
         <v>45481</v>
       </c>
       <c r="P22" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q22" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R22" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S22" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U22" s="1">
         <v>45481</v>
       </c>
       <c r="X22" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y22" s="7">
-        <v>46260</v>
-      </c>
-      <c r="Z22" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y22)-IF(MONTH(Y22)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y22),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Y22" s="7"/>
       <c r="AA22" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AD22" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG22" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:33">
       <c r="A23">
         <v>105722</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C23" t="s">
-        <v>35</v>
+        <v>162</v>
       </c>
       <c r="D23" t="s">
-        <v>36</v>
+        <v>163</v>
       </c>
       <c r="E23" t="s">
+        <v>164</v>
+      </c>
+      <c r="F23" t="s">
         <v>37</v>
       </c>
-      <c r="F23" t="s">
-        <v>38</v>
-      </c>
       <c r="G23" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="H23" t="s">
-        <v>39</v>
+        <v>165</v>
       </c>
       <c r="I23" t="s">
-        <v>40</v>
+        <v>166</v>
       </c>
       <c r="J23" t="s">
-        <v>41</v>
+        <v>167</v>
       </c>
       <c r="K23" t="s">
-        <v>42</v>
+        <v>168</v>
       </c>
       <c r="L23" t="s">
-        <v>43</v>
+        <v>169</v>
       </c>
       <c r="M23" t="s">
+        <v>126</v>
+      </c>
+      <c r="N23" t="s">
         <v>44</v>
-      </c>
-      <c r="N23" t="s">
-        <v>32</v>
       </c>
       <c r="O23" s="1">
         <v>34169</v>
       </c>
       <c r="P23" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q23" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R23" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S23" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U23" s="1">
         <v>44343</v>
@@ -4002,1191 +3867,1095 @@
         <v>FY2025 Q4</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y23" s="7">
-        <v>46225</v>
-      </c>
-      <c r="Z23" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y23)-IF(MONTH(Y23)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y23),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="Y23" s="7"/>
       <c r="AA23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB23" s="7">
-        <v>46190</v>
-      </c>
-      <c r="AC23" s="2" t="str">
-        <f>"FY"&amp;YEAR(AB23)-IF(MONTH(AB23)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(AB23),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q1</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="AB23" s="7"/>
       <c r="AD23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="AE23" s="7">
-        <v>46248</v>
-      </c>
-      <c r="AF23" s="2" t="str">
-        <f>"FY"&amp;YEAR(AE23)-IF(MONTH(AE23)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(AE23),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="AE23" s="7"/>
       <c r="AG23" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:33">
       <c r="A24">
         <v>106138</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C24" t="s">
-        <v>81</v>
+        <v>170</v>
       </c>
       <c r="D24" t="s">
-        <v>82</v>
+        <v>171</v>
       </c>
       <c r="E24" t="s">
-        <v>83</v>
+        <v>172</v>
       </c>
       <c r="F24" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="G24" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="H24" t="s">
-        <v>39</v>
+        <v>165</v>
       </c>
       <c r="I24" t="s">
-        <v>84</v>
+        <v>173</v>
       </c>
       <c r="J24" t="s">
-        <v>41</v>
+        <v>167</v>
       </c>
       <c r="K24" t="s">
-        <v>42</v>
+        <v>168</v>
       </c>
       <c r="L24" t="s">
-        <v>43</v>
+        <v>169</v>
       </c>
       <c r="M24" t="s">
+        <v>126</v>
+      </c>
+      <c r="N24" t="s">
         <v>44</v>
-      </c>
-      <c r="N24" t="s">
-        <v>32</v>
       </c>
       <c r="O24" s="1">
         <v>35492</v>
       </c>
       <c r="P24" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q24" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R24" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S24" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U24" s="1">
         <v>44343</v>
       </c>
       <c r="X24" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y24" s="7">
-        <v>46232</v>
-      </c>
-      <c r="Z24" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y24)-IF(MONTH(Y24)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y24),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Y24" s="7"/>
       <c r="AA24" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AD24" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG24" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:33">
       <c r="A25">
         <v>126536</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C25" t="s">
+        <v>174</v>
+      </c>
+      <c r="D25" t="s">
+        <v>175</v>
+      </c>
+      <c r="E25" t="s">
+        <v>176</v>
+      </c>
+      <c r="F25" t="s">
+        <v>37</v>
+      </c>
+      <c r="G25" t="s">
+        <v>79</v>
+      </c>
+      <c r="H25" t="s">
+        <v>165</v>
+      </c>
+      <c r="I25" t="s">
+        <v>177</v>
+      </c>
+      <c r="J25" t="s">
+        <v>167</v>
+      </c>
+      <c r="K25" t="s">
+        <v>168</v>
+      </c>
+      <c r="L25" t="s">
+        <v>169</v>
+      </c>
+      <c r="M25" t="s">
         <v>126</v>
       </c>
-      <c r="D25" t="s">
-        <v>127</v>
-      </c>
-      <c r="E25" t="s">
-        <v>128</v>
-      </c>
-      <c r="F25" t="s">
-        <v>38</v>
-      </c>
-      <c r="G25" t="s">
-        <v>25</v>
-      </c>
-      <c r="H25" t="s">
-        <v>39</v>
-      </c>
-      <c r="I25" t="s">
-        <v>129</v>
-      </c>
-      <c r="J25" t="s">
-        <v>41</v>
-      </c>
-      <c r="K25" t="s">
-        <v>42</v>
-      </c>
-      <c r="L25" t="s">
-        <v>43</v>
-      </c>
-      <c r="M25" t="s">
+      <c r="N25" t="s">
         <v>44</v>
-      </c>
-      <c r="N25" t="s">
-        <v>32</v>
       </c>
       <c r="O25" s="1">
         <v>45035</v>
       </c>
       <c r="P25" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q25" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R25" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S25" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U25" s="1">
         <v>45051</v>
       </c>
       <c r="X25" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y25" s="7">
-        <v>46240</v>
-      </c>
-      <c r="Z25" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y25)-IF(MONTH(Y25)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y25),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Y25" s="7"/>
       <c r="AA25" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AD25" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG25" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:33">
       <c r="A26">
         <v>122812</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C26" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="D26" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="E26" t="s">
+        <v>180</v>
+      </c>
+      <c r="F26" t="s">
+        <v>52</v>
+      </c>
+      <c r="G26" t="s">
+        <v>79</v>
+      </c>
+      <c r="H26" t="s">
         <v>165</v>
       </c>
-      <c r="F26" t="s">
-        <v>69</v>
-      </c>
-      <c r="G26" t="s">
-        <v>25</v>
-      </c>
-      <c r="H26" t="s">
-        <v>39</v>
-      </c>
       <c r="I26" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="J26" t="s">
-        <v>41</v>
+        <v>167</v>
       </c>
       <c r="K26" t="s">
-        <v>42</v>
+        <v>168</v>
       </c>
       <c r="L26" t="s">
-        <v>43</v>
+        <v>169</v>
       </c>
       <c r="M26" t="s">
+        <v>126</v>
+      </c>
+      <c r="N26" t="s">
         <v>44</v>
-      </c>
-      <c r="N26" t="s">
-        <v>32</v>
       </c>
       <c r="O26" s="1">
         <v>43557</v>
       </c>
       <c r="P26" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q26" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R26" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S26" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U26" s="1">
         <v>44327</v>
       </c>
       <c r="X26" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y26" s="7">
-        <v>46246</v>
-      </c>
-      <c r="Z26" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y26)-IF(MONTH(Y26)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y26),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Y26" s="7"/>
       <c r="AA26" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AD26" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG26" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:33">
       <c r="A27">
         <v>103467</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C27" t="s">
-        <v>167</v>
+        <v>101</v>
       </c>
       <c r="D27" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="E27" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="F27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G27" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="H27" t="s">
-        <v>39</v>
+        <v>165</v>
       </c>
       <c r="I27" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="J27" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="K27" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="L27" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="M27" t="s">
+        <v>126</v>
+      </c>
+      <c r="N27" t="s">
         <v>44</v>
-      </c>
-      <c r="N27" t="s">
-        <v>32</v>
       </c>
       <c r="O27" s="1">
         <v>30769</v>
       </c>
       <c r="P27" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q27" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R27" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S27" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U27" s="1">
         <v>44343</v>
       </c>
       <c r="X27" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y27" s="7">
-        <v>46248</v>
-      </c>
-      <c r="Z27" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y27)-IF(MONTH(Y27)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y27),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Y27" s="7"/>
       <c r="AA27" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AD27" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG27" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:33">
       <c r="A28">
         <v>128969</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C28" t="s">
-        <v>99</v>
+        <v>188</v>
       </c>
       <c r="D28" t="s">
-        <v>100</v>
+        <v>189</v>
       </c>
       <c r="E28" t="s">
-        <v>101</v>
+        <v>190</v>
       </c>
       <c r="F28" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="G28" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="H28" t="s">
-        <v>102</v>
+        <v>191</v>
       </c>
       <c r="I28" t="s">
-        <v>102</v>
+        <v>191</v>
       </c>
       <c r="J28" t="s">
-        <v>103</v>
+        <v>192</v>
       </c>
       <c r="K28" t="s">
-        <v>104</v>
+        <v>193</v>
       </c>
       <c r="L28" t="s">
-        <v>105</v>
+        <v>194</v>
       </c>
       <c r="M28" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="N28" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O28" s="1">
         <v>45922</v>
       </c>
       <c r="P28" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q28" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R28" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S28" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U28" s="1">
         <v>45922</v>
       </c>
       <c r="X28" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y28" s="7">
-        <v>46235</v>
-      </c>
-      <c r="Z28" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y28)-IF(MONTH(Y28)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y28),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Y28" s="7"/>
       <c r="AA28" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AD28" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG28" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:33">
       <c r="A29">
         <v>126904</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C29" t="s">
-        <v>109</v>
+        <v>195</v>
       </c>
       <c r="D29" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="E29" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="F29" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="G29" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="H29" t="s">
-        <v>102</v>
+        <v>191</v>
       </c>
       <c r="I29" t="s">
-        <v>102</v>
+        <v>191</v>
       </c>
       <c r="J29" t="s">
-        <v>103</v>
+        <v>192</v>
       </c>
       <c r="K29" t="s">
-        <v>104</v>
+        <v>193</v>
       </c>
       <c r="L29" t="s">
-        <v>105</v>
+        <v>194</v>
       </c>
       <c r="M29" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="N29" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O29" s="1">
         <v>45159</v>
       </c>
       <c r="P29" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q29" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R29" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S29" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T29" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U29" s="1">
         <v>45170</v>
       </c>
       <c r="X29" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y29" s="7">
-        <v>46237</v>
-      </c>
-      <c r="Z29" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y29)-IF(MONTH(Y29)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y29),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Y29" s="7"/>
       <c r="AA29" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AD29" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG29" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:33">
       <c r="A30">
         <v>127802</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C30" t="s">
-        <v>190</v>
+        <v>59</v>
       </c>
       <c r="D30" t="s">
+        <v>198</v>
+      </c>
+      <c r="E30" t="s">
+        <v>199</v>
+      </c>
+      <c r="F30" t="s">
+        <v>52</v>
+      </c>
+      <c r="G30" t="s">
+        <v>38</v>
+      </c>
+      <c r="H30" t="s">
         <v>191</v>
       </c>
-      <c r="E30" t="s">
+      <c r="I30" t="s">
+        <v>191</v>
+      </c>
+      <c r="J30" t="s">
         <v>192</v>
       </c>
-      <c r="F30" t="s">
-        <v>69</v>
-      </c>
-      <c r="G30" t="s">
-        <v>58</v>
-      </c>
-      <c r="H30" t="s">
-        <v>102</v>
-      </c>
-      <c r="I30" t="s">
-        <v>102</v>
-      </c>
-      <c r="J30" t="s">
-        <v>103</v>
-      </c>
       <c r="K30" t="s">
-        <v>104</v>
+        <v>193</v>
       </c>
       <c r="L30" t="s">
-        <v>105</v>
+        <v>194</v>
       </c>
       <c r="M30" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="N30" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O30" s="1">
         <v>45467</v>
       </c>
       <c r="P30" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q30" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R30" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S30" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T30" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U30" s="1">
         <v>45467</v>
       </c>
       <c r="X30" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y30" s="7">
-        <v>46252</v>
-      </c>
-      <c r="Z30" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y30)-IF(MONTH(Y30)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y30),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Y30" s="7"/>
       <c r="AA30" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AD30" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG30" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:33">
       <c r="A31">
         <v>124636</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C31" t="s">
-        <v>91</v>
+        <v>200</v>
       </c>
       <c r="D31" t="s">
-        <v>92</v>
+        <v>201</v>
       </c>
       <c r="E31" t="s">
-        <v>93</v>
+        <v>202</v>
       </c>
       <c r="F31" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G31" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="H31" t="s">
-        <v>94</v>
+        <v>203</v>
       </c>
       <c r="I31" t="s">
-        <v>95</v>
+        <v>204</v>
       </c>
       <c r="J31" t="s">
-        <v>96</v>
+        <v>205</v>
       </c>
       <c r="K31" t="s">
-        <v>97</v>
+        <v>206</v>
       </c>
       <c r="L31" t="s">
-        <v>98</v>
+        <v>207</v>
       </c>
       <c r="M31" t="s">
+        <v>126</v>
+      </c>
+      <c r="N31" t="s">
         <v>44</v>
-      </c>
-      <c r="N31" t="s">
-        <v>32</v>
       </c>
       <c r="O31" s="1">
         <v>44396</v>
       </c>
       <c r="P31" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q31" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R31" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S31" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U31" s="1">
         <v>44796</v>
       </c>
       <c r="X31" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y31" s="7">
-        <v>46234</v>
-      </c>
-      <c r="Z31" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y31)-IF(MONTH(Y31)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y31),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Y31" s="7"/>
       <c r="AA31" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AD31" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG31" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:33">
       <c r="A32">
         <v>126110</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C32" t="s">
-        <v>130</v>
+        <v>208</v>
       </c>
       <c r="D32" t="s">
-        <v>131</v>
+        <v>209</v>
       </c>
       <c r="E32" t="s">
-        <v>132</v>
+        <v>210</v>
       </c>
       <c r="F32" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="G32" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="H32" t="s">
-        <v>94</v>
+        <v>203</v>
       </c>
       <c r="I32" t="s">
-        <v>94</v>
+        <v>203</v>
       </c>
       <c r="J32" t="s">
-        <v>133</v>
+        <v>211</v>
       </c>
       <c r="K32" t="s">
-        <v>134</v>
+        <v>212</v>
       </c>
       <c r="L32" t="s">
-        <v>135</v>
+        <v>213</v>
       </c>
       <c r="M32" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="N32" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O32" s="1">
         <v>44900</v>
       </c>
       <c r="P32" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q32" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R32" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S32" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U32" s="1">
         <v>44908</v>
       </c>
       <c r="X32" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y32" s="7">
-        <v>46241</v>
-      </c>
-      <c r="Z32" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y32)-IF(MONTH(Y32)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y32),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Y32" s="7"/>
       <c r="AA32" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AD32" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG32" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:33">
       <c r="A33">
         <v>129148</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C33" t="s">
-        <v>150</v>
+        <v>214</v>
       </c>
       <c r="D33" t="s">
-        <v>151</v>
+        <v>215</v>
       </c>
       <c r="E33" t="s">
-        <v>152</v>
+        <v>216</v>
       </c>
       <c r="F33" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="G33" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="H33" t="s">
-        <v>94</v>
+        <v>203</v>
       </c>
       <c r="I33" t="s">
-        <v>153</v>
+        <v>217</v>
       </c>
       <c r="J33" t="s">
-        <v>154</v>
+        <v>218</v>
       </c>
       <c r="K33" t="s">
-        <v>155</v>
+        <v>219</v>
       </c>
       <c r="L33" t="s">
-        <v>156</v>
+        <v>220</v>
       </c>
       <c r="M33" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="N33" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O33" s="1">
         <v>45999</v>
       </c>
       <c r="P33" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q33" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R33" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S33" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U33" s="1">
         <v>45999</v>
       </c>
       <c r="X33" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y33" s="7">
-        <v>46244</v>
-      </c>
-      <c r="Z33" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y33)-IF(MONTH(Y33)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y33),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Y33" s="7"/>
       <c r="AA33" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AD33" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG33" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:33">
       <c r="A34">
         <v>115424</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C34" t="s">
-        <v>181</v>
+        <v>221</v>
       </c>
       <c r="D34" t="s">
-        <v>182</v>
+        <v>222</v>
       </c>
       <c r="E34" t="s">
-        <v>183</v>
+        <v>223</v>
       </c>
       <c r="F34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G34" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="H34" t="s">
-        <v>94</v>
+        <v>203</v>
       </c>
       <c r="I34" t="s">
-        <v>95</v>
+        <v>204</v>
       </c>
       <c r="J34" t="s">
-        <v>96</v>
+        <v>205</v>
       </c>
       <c r="K34" t="s">
-        <v>97</v>
+        <v>206</v>
       </c>
       <c r="L34" t="s">
-        <v>98</v>
+        <v>207</v>
       </c>
       <c r="M34" t="s">
+        <v>126</v>
+      </c>
+      <c r="N34" t="s">
         <v>44</v>
-      </c>
-      <c r="N34" t="s">
-        <v>32</v>
       </c>
       <c r="O34" s="1">
         <v>41456</v>
       </c>
       <c r="P34" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q34" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R34" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S34" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U34" s="1">
         <v>44323</v>
       </c>
       <c r="X34" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y34" s="7">
-        <v>46250</v>
-      </c>
-      <c r="Z34" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y34)-IF(MONTH(Y34)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y34),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Y34" s="7"/>
       <c r="AA34" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AD34" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG34" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:33">
       <c r="A35">
         <v>129309</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D35" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E35" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F35" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="G35" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s">
-        <v>94</v>
+        <v>203</v>
       </c>
       <c r="I35" t="s">
-        <v>94</v>
+        <v>203</v>
       </c>
       <c r="J35" t="s">
-        <v>133</v>
+        <v>211</v>
       </c>
       <c r="K35" t="s">
-        <v>134</v>
+        <v>212</v>
       </c>
       <c r="L35" t="s">
-        <v>135</v>
+        <v>213</v>
       </c>
       <c r="M35" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="N35" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O35" s="1">
         <v>46113</v>
       </c>
       <c r="P35" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q35" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R35" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S35" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U35" s="1">
         <v>46113</v>
       </c>
       <c r="X35" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y35" s="7">
-        <v>46261</v>
-      </c>
-      <c r="Z35" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y35)-IF(MONTH(Y35)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y35),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Y35" s="7"/>
       <c r="AA35" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AD35" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG35" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:33">
       <c r="A36">
         <v>126595</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C36" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="D36" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="E36" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="F36" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="G36" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="H36" t="s">
-        <v>94</v>
+        <v>203</v>
       </c>
       <c r="I36" t="s">
-        <v>95</v>
+        <v>204</v>
       </c>
       <c r="J36" t="s">
-        <v>96</v>
+        <v>205</v>
       </c>
       <c r="K36" t="s">
-        <v>97</v>
+        <v>206</v>
       </c>
       <c r="L36" t="s">
-        <v>98</v>
+        <v>207</v>
       </c>
       <c r="M36" t="s">
+        <v>126</v>
+      </c>
+      <c r="N36" t="s">
         <v>44</v>
-      </c>
-      <c r="N36" t="s">
-        <v>32</v>
       </c>
       <c r="O36" s="1">
         <v>45069</v>
       </c>
       <c r="P36" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q36" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R36" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S36" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U36" s="1">
         <v>45070</v>
       </c>
       <c r="X36" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y36" s="7">
-        <v>46263</v>
-      </c>
-      <c r="Z36" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y36)-IF(MONTH(Y36)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y36),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Y36" s="7"/>
       <c r="AA36" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AD36" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG36" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:33">
       <c r="A37">
         <v>123471</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C37" t="s">
-        <v>55</v>
+        <v>230</v>
       </c>
       <c r="D37" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="E37" t="s">
-        <v>57</v>
+        <v>231</v>
       </c>
       <c r="F37" t="s">
+        <v>37</v>
+      </c>
+      <c r="G37" t="s">
         <v>38</v>
       </c>
-      <c r="G37" t="s">
-        <v>58</v>
-      </c>
       <c r="H37" t="s">
-        <v>59</v>
+        <v>232</v>
       </c>
       <c r="I37" t="s">
-        <v>59</v>
+        <v>232</v>
       </c>
       <c r="J37" t="s">
-        <v>60</v>
+        <v>233</v>
       </c>
       <c r="K37" t="s">
-        <v>61</v>
+        <v>234</v>
       </c>
       <c r="L37" t="s">
-        <v>62</v>
+        <v>235</v>
       </c>
       <c r="M37" t="s">
+        <v>126</v>
+      </c>
+      <c r="N37" t="s">
         <v>44</v>
-      </c>
-      <c r="N37" t="s">
-        <v>32</v>
       </c>
       <c r="O37" s="1">
         <v>43753</v>
       </c>
       <c r="P37" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q37" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R37" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S37" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T37" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U37" s="1">
         <v>44330</v>
@@ -5199,388 +4968,358 @@
         <v>FY2025 Q4</v>
       </c>
       <c r="X37" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y37" s="7">
-        <v>46227</v>
-      </c>
-      <c r="Z37" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y37)-IF(MONTH(Y37)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y37),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="Y37" s="7"/>
       <c r="AA37" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AD37" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG37" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:33">
       <c r="A38">
         <v>128192</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C38" t="s">
-        <v>63</v>
+        <v>139</v>
       </c>
       <c r="D38" t="s">
-        <v>64</v>
+        <v>236</v>
       </c>
       <c r="E38" t="s">
-        <v>65</v>
+        <v>237</v>
       </c>
       <c r="F38" t="s">
+        <v>37</v>
+      </c>
+      <c r="G38" t="s">
         <v>38</v>
       </c>
-      <c r="G38" t="s">
-        <v>58</v>
-      </c>
       <c r="H38" t="s">
-        <v>59</v>
+        <v>232</v>
       </c>
       <c r="I38" t="s">
-        <v>59</v>
+        <v>232</v>
       </c>
       <c r="J38" t="s">
-        <v>60</v>
+        <v>233</v>
       </c>
       <c r="K38" t="s">
-        <v>61</v>
+        <v>234</v>
       </c>
       <c r="L38" t="s">
-        <v>62</v>
+        <v>235</v>
       </c>
       <c r="M38" t="s">
+        <v>126</v>
+      </c>
+      <c r="N38" t="s">
         <v>44</v>
-      </c>
-      <c r="N38" t="s">
-        <v>32</v>
       </c>
       <c r="O38" s="1">
         <v>45607</v>
       </c>
       <c r="P38" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q38" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R38" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S38" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U38" s="1">
         <v>45607</v>
       </c>
       <c r="X38" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y38" s="7">
-        <v>46228</v>
-      </c>
-      <c r="Z38" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y38)-IF(MONTH(Y38)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y38),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Y38" s="7"/>
       <c r="AA38" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AD38" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG38" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:33">
       <c r="A39">
         <v>104738</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C39" t="s">
-        <v>78</v>
+        <v>238</v>
       </c>
       <c r="D39" t="s">
-        <v>79</v>
+        <v>239</v>
       </c>
       <c r="E39" t="s">
-        <v>80</v>
+        <v>240</v>
       </c>
       <c r="F39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G39" t="s">
         <v>38</v>
       </c>
-      <c r="G39" t="s">
-        <v>58</v>
-      </c>
       <c r="H39" t="s">
-        <v>59</v>
+        <v>232</v>
       </c>
       <c r="I39" t="s">
-        <v>59</v>
+        <v>232</v>
       </c>
       <c r="J39" t="s">
-        <v>60</v>
+        <v>233</v>
       </c>
       <c r="K39" t="s">
-        <v>61</v>
+        <v>234</v>
       </c>
       <c r="L39" t="s">
-        <v>62</v>
+        <v>235</v>
       </c>
       <c r="M39" t="s">
+        <v>126</v>
+      </c>
+      <c r="N39" t="s">
         <v>44</v>
-      </c>
-      <c r="N39" t="s">
-        <v>32</v>
       </c>
       <c r="O39" s="1">
         <v>39335</v>
       </c>
       <c r="P39" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q39" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R39" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S39" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U39" s="1">
         <v>44343</v>
       </c>
       <c r="X39" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y39" s="7">
-        <v>46231</v>
-      </c>
-      <c r="Z39" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y39)-IF(MONTH(Y39)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y39),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Y39" s="7"/>
       <c r="AA39" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AD39" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG39" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:33">
       <c r="A40">
         <v>127709</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C40" t="s">
-        <v>144</v>
+        <v>241</v>
       </c>
       <c r="D40" t="s">
-        <v>145</v>
+        <v>242</v>
       </c>
       <c r="E40" t="s">
-        <v>146</v>
+        <v>243</v>
       </c>
       <c r="F40" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G40" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="H40" t="s">
-        <v>59</v>
+        <v>232</v>
       </c>
       <c r="I40" t="s">
-        <v>59</v>
+        <v>232</v>
       </c>
       <c r="J40" t="s">
-        <v>147</v>
+        <v>244</v>
       </c>
       <c r="K40" t="s">
-        <v>148</v>
+        <v>245</v>
       </c>
       <c r="L40" t="s">
-        <v>149</v>
+        <v>246</v>
       </c>
       <c r="M40" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="N40" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O40" s="1">
         <v>45440</v>
       </c>
       <c r="P40" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q40" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R40" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S40" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U40" s="1">
         <v>45440</v>
       </c>
       <c r="X40" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y40" s="7">
-        <v>46243</v>
-      </c>
-      <c r="Z40" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y40)-IF(MONTH(Y40)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y40),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Y40" s="7"/>
       <c r="AA40" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AD40" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG40" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:33">
       <c r="A41">
         <v>127904</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C41" t="s">
-        <v>157</v>
+        <v>247</v>
       </c>
       <c r="D41" t="s">
-        <v>158</v>
+        <v>248</v>
       </c>
       <c r="E41" t="s">
-        <v>159</v>
+        <v>249</v>
       </c>
       <c r="F41" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G41" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="H41" t="s">
-        <v>59</v>
+        <v>232</v>
       </c>
       <c r="I41" t="s">
-        <v>59</v>
+        <v>232</v>
       </c>
       <c r="J41" t="s">
-        <v>160</v>
+        <v>250</v>
       </c>
       <c r="K41" t="s">
-        <v>161</v>
+        <v>251</v>
       </c>
       <c r="L41" t="s">
-        <v>162</v>
+        <v>252</v>
       </c>
       <c r="M41" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="N41" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O41" s="1">
         <v>45538</v>
       </c>
       <c r="P41" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q41" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R41" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S41" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U41" s="1">
         <v>45553</v>
       </c>
       <c r="X41" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y41" s="7">
-        <v>46245</v>
-      </c>
-      <c r="Z41" s="2" t="str">
-        <f>"FY"&amp;YEAR(Y41)-IF(MONTH(Y41)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(Y41),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Y41" s="7"/>
       <c r="AA41" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AD41" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG41" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:33">
       <c r="A42">
         <v>125769</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C42" t="s">
-        <v>187</v>
+        <v>53</v>
       </c>
       <c r="D42" t="s">
-        <v>188</v>
+        <v>54</v>
       </c>
       <c r="E42" t="s">
-        <v>189</v>
+        <v>55</v>
       </c>
       <c r="F42" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="G42" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="H42" t="s">
-        <v>115</v>
+        <v>39</v>
       </c>
       <c r="I42" t="s">
-        <v>115</v>
+        <v>39</v>
       </c>
       <c r="J42" t="s">
         <v>253</v>
@@ -5595,66 +5334,66 @@
         <v>256</v>
       </c>
       <c r="N42" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O42" s="1" t="s">
         <v>257</v>
       </c>
       <c r="P42" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q42" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R42" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S42" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T42" s="2" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="X42" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AA42" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AD42" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG42" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:33">
       <c r="A43">
         <v>121571</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C43" t="s">
-        <v>190</v>
+        <v>59</v>
       </c>
       <c r="D43" t="s">
-        <v>212</v>
+        <v>60</v>
       </c>
       <c r="E43" t="s">
-        <v>213</v>
+        <v>61</v>
       </c>
       <c r="F43" t="s">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="G43" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="H43" t="s">
-        <v>115</v>
+        <v>39</v>
       </c>
       <c r="I43" t="s">
-        <v>115</v>
+        <v>39</v>
       </c>
       <c r="J43" t="s">
         <v>253</v>
@@ -5669,66 +5408,66 @@
         <v>256</v>
       </c>
       <c r="N43" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O43" s="1" t="s">
         <v>258</v>
       </c>
       <c r="P43" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q43" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R43" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S43" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T43" s="2" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="X43" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AA43" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AD43" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG43" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:33">
       <c r="A44">
         <v>111249</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C44" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="D44" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="E44" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F44" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="G44" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="H44" t="s">
-        <v>115</v>
+        <v>39</v>
       </c>
       <c r="I44" t="s">
-        <v>115</v>
+        <v>39</v>
       </c>
       <c r="J44" t="s">
         <v>259</v>
@@ -5743,60 +5482,60 @@
         <v>262</v>
       </c>
       <c r="N44" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O44" s="1" t="s">
         <v>263</v>
       </c>
       <c r="P44" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q44" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R44" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S44" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T44" s="2" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="X44" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AA44" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AD44" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG44" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:33">
       <c r="A45">
         <v>116603</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C45" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="D45" t="s">
-        <v>29</v>
+        <v>83</v>
       </c>
       <c r="E45" t="s">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="F45" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="G45" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="H45" t="s">
         <v>264</v>
@@ -5805,7 +5544,7 @@
         <v>264</v>
       </c>
       <c r="J45" t="s">
-        <v>187</v>
+        <v>53</v>
       </c>
       <c r="K45" t="s">
         <v>265</v>
@@ -5817,60 +5556,60 @@
         <v>267</v>
       </c>
       <c r="N45" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O45" s="1" t="s">
         <v>268</v>
       </c>
       <c r="P45" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q45" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R45" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S45" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T45" s="2" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="X45" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AA45" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AD45" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG45" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:33">
       <c r="A46">
         <v>123220</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C46" t="s">
-        <v>222</v>
+        <v>90</v>
       </c>
       <c r="D46" t="s">
-        <v>223</v>
+        <v>91</v>
       </c>
       <c r="E46" t="s">
-        <v>224</v>
+        <v>92</v>
       </c>
       <c r="F46" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="G46" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="H46" t="s">
         <v>264</v>
@@ -5879,7 +5618,7 @@
         <v>264</v>
       </c>
       <c r="J46" t="s">
-        <v>167</v>
+        <v>101</v>
       </c>
       <c r="K46" t="s">
         <v>269</v>
@@ -5891,60 +5630,60 @@
         <v>256</v>
       </c>
       <c r="N46" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O46" s="1" t="s">
         <v>271</v>
       </c>
       <c r="P46" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q46" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R46" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S46" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T46" s="2" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="X46" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AA46" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AD46" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG46" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:33">
       <c r="A47">
         <v>111259</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C47" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="D47" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="E47" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="F47" t="s">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="G47" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="H47" t="s">
         <v>272</v>
@@ -5965,66 +5704,66 @@
         <v>276</v>
       </c>
       <c r="N47" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O47" s="1" t="s">
         <v>277</v>
       </c>
       <c r="P47" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q47" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R47" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S47" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T47" s="2" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="X47" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AA47" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AD47" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG47" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:33">
       <c r="A48">
         <v>103915</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C48" t="s">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="D48" t="s">
-        <v>141</v>
+        <v>106</v>
       </c>
       <c r="E48" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="F48" t="s">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="G48" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="H48" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="I48" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="J48" t="s">
         <v>278</v>
@@ -6039,134 +5778,134 @@
         <v>281</v>
       </c>
       <c r="N48" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O48" s="1" t="s">
         <v>282</v>
       </c>
       <c r="P48" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q48" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R48" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S48" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T48" s="2" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="X48" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AA48" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AD48" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG48" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="49" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:33">
       <c r="A49">
         <v>121515</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C49" t="s">
-        <v>206</v>
+        <v>123</v>
       </c>
       <c r="D49" t="s">
-        <v>207</v>
+        <v>124</v>
       </c>
       <c r="E49" t="s">
-        <v>208</v>
+        <v>125</v>
       </c>
       <c r="F49" t="s">
+        <v>126</v>
+      </c>
+      <c r="G49" t="s">
+        <v>38</v>
+      </c>
+      <c r="H49" t="s">
+        <v>116</v>
+      </c>
+      <c r="I49" t="s">
+        <v>116</v>
+      </c>
+      <c r="J49" t="s">
+        <v>105</v>
+      </c>
+      <c r="K49" t="s">
+        <v>106</v>
+      </c>
+      <c r="L49" t="s">
+        <v>107</v>
+      </c>
+      <c r="M49" t="s">
+        <v>108</v>
+      </c>
+      <c r="N49" t="s">
         <v>44</v>
-      </c>
-      <c r="G49" t="s">
-        <v>58</v>
-      </c>
-      <c r="H49" t="s">
-        <v>139</v>
-      </c>
-      <c r="I49" t="s">
-        <v>139</v>
-      </c>
-      <c r="J49" t="s">
-        <v>140</v>
-      </c>
-      <c r="K49" t="s">
-        <v>141</v>
-      </c>
-      <c r="L49" t="s">
-        <v>142</v>
-      </c>
-      <c r="M49" t="s">
-        <v>143</v>
-      </c>
-      <c r="N49" t="s">
-        <v>32</v>
       </c>
       <c r="O49" s="1" t="s">
         <v>283</v>
       </c>
       <c r="P49" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q49" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R49" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S49" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T49" s="2" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="X49" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AA49" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AD49" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG49" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:33">
       <c r="A50">
         <v>123690</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C50" t="s">
-        <v>72</v>
+        <v>132</v>
       </c>
       <c r="D50" t="s">
+        <v>133</v>
+      </c>
+      <c r="E50" t="s">
+        <v>134</v>
+      </c>
+      <c r="F50" t="s">
         <v>73</v>
       </c>
-      <c r="E50" t="s">
-        <v>74</v>
-      </c>
-      <c r="F50" t="s">
-        <v>54</v>
-      </c>
       <c r="G50" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="H50" t="s">
         <v>272</v>
@@ -6187,60 +5926,60 @@
         <v>276</v>
       </c>
       <c r="N50" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O50" s="1" t="s">
         <v>284</v>
       </c>
       <c r="P50" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q50" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R50" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S50" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T50" s="2" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="X50" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AA50" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AD50" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG50" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="51" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:33">
       <c r="A51">
         <v>101989</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C51" t="s">
-        <v>63</v>
+        <v>139</v>
       </c>
       <c r="D51" t="s">
-        <v>89</v>
+        <v>140</v>
       </c>
       <c r="E51" t="s">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="F51" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="G51" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="H51" t="s">
         <v>272</v>
@@ -6261,60 +6000,60 @@
         <v>256</v>
       </c>
       <c r="N51" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O51" s="1" t="s">
         <v>288</v>
       </c>
       <c r="P51" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q51" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R51" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S51" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T51" s="2" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="X51" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AA51" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AD51" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG51" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="52" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:33">
       <c r="A52">
         <v>119635</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C52" t="s">
-        <v>41</v>
+        <v>167</v>
       </c>
       <c r="D52" t="s">
-        <v>42</v>
+        <v>168</v>
       </c>
       <c r="E52" t="s">
-        <v>43</v>
+        <v>169</v>
       </c>
       <c r="F52" t="s">
-        <v>44</v>
+        <v>126</v>
       </c>
       <c r="G52" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="H52" t="s">
         <v>264</v>
@@ -6326,7 +6065,7 @@
         <v>289</v>
       </c>
       <c r="K52" t="s">
-        <v>42</v>
+        <v>168</v>
       </c>
       <c r="L52" t="s">
         <v>290</v>
@@ -6335,60 +6074,60 @@
         <v>291</v>
       </c>
       <c r="N52" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O52" s="1" t="s">
         <v>292</v>
       </c>
       <c r="P52" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q52" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R52" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S52" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T52" s="2" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="X52" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AA52" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AD52" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG52" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="53" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:33">
       <c r="A53">
         <v>126338</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C53" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D53" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E53" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="F53" t="s">
-        <v>44</v>
+        <v>126</v>
       </c>
       <c r="G53" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="H53" t="s">
         <v>264</v>
@@ -6409,69 +6148,69 @@
         <v>267</v>
       </c>
       <c r="N53" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O53" s="1" t="s">
         <v>296</v>
       </c>
       <c r="P53" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q53" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R53" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S53" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T53" s="2" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="X53" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AA53" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AD53" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG53" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="54" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:33">
       <c r="A54">
         <v>129427</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C54" t="s">
-        <v>103</v>
+        <v>192</v>
       </c>
       <c r="D54" t="s">
-        <v>104</v>
+        <v>193</v>
       </c>
       <c r="E54" t="s">
-        <v>105</v>
+        <v>194</v>
       </c>
       <c r="F54" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="G54" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="H54" t="s">
-        <v>102</v>
+        <v>191</v>
       </c>
       <c r="I54" t="s">
-        <v>102</v>
+        <v>191</v>
       </c>
       <c r="J54" t="s">
-        <v>187</v>
+        <v>53</v>
       </c>
       <c r="K54" t="s">
         <v>297</v>
@@ -6483,66 +6222,66 @@
         <v>276</v>
       </c>
       <c r="N54" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O54" s="1" t="s">
         <v>299</v>
       </c>
       <c r="P54" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q54" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R54" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S54" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T54" s="2" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="X54" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AA54" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AD54" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG54" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="55" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:33">
       <c r="A55">
         <v>118764</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C55" t="s">
-        <v>96</v>
+        <v>205</v>
       </c>
       <c r="D55" t="s">
-        <v>97</v>
+        <v>206</v>
       </c>
       <c r="E55" t="s">
-        <v>98</v>
+        <v>207</v>
       </c>
       <c r="F55" t="s">
-        <v>44</v>
+        <v>126</v>
       </c>
       <c r="G55" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="H55" t="s">
-        <v>115</v>
+        <v>39</v>
       </c>
       <c r="I55" t="s">
-        <v>115</v>
+        <v>39</v>
       </c>
       <c r="J55" t="s">
         <v>300</v>
@@ -6557,66 +6296,66 @@
         <v>267</v>
       </c>
       <c r="N55" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O55" s="1" t="s">
         <v>303</v>
       </c>
       <c r="P55" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q55" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R55" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S55" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T55" s="2" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="X55" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AA55" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AD55" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG55" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="56" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:33">
       <c r="A56">
         <v>126128</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C56" t="s">
-        <v>133</v>
+        <v>211</v>
       </c>
       <c r="D56" t="s">
-        <v>134</v>
+        <v>212</v>
       </c>
       <c r="E56" t="s">
-        <v>135</v>
+        <v>213</v>
       </c>
       <c r="F56" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="G56" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="H56" t="s">
-        <v>115</v>
+        <v>39</v>
       </c>
       <c r="I56" t="s">
-        <v>115</v>
+        <v>39</v>
       </c>
       <c r="J56" t="s">
         <v>304</v>
@@ -6631,66 +6370,66 @@
         <v>256</v>
       </c>
       <c r="N56" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O56" s="1" t="s">
         <v>307</v>
       </c>
       <c r="P56" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q56" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R56" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S56" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T56" s="2" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="X56" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AA56" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AD56" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG56" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="57" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:33">
       <c r="A57">
         <v>126291</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C57" t="s">
-        <v>154</v>
+        <v>218</v>
       </c>
       <c r="D57" t="s">
-        <v>155</v>
+        <v>219</v>
       </c>
       <c r="E57" t="s">
-        <v>156</v>
+        <v>220</v>
       </c>
       <c r="F57" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="G57" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="H57" t="s">
-        <v>115</v>
+        <v>39</v>
       </c>
       <c r="I57" t="s">
-        <v>115</v>
+        <v>39</v>
       </c>
       <c r="J57" t="s">
         <v>304</v>
@@ -6705,72 +6444,72 @@
         <v>256</v>
       </c>
       <c r="N57" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O57" s="1" t="s">
         <v>308</v>
       </c>
       <c r="P57" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q57" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R57" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S57" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T57" s="2" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="X57" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AA57" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AD57" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG57" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="58" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:33">
       <c r="A58">
         <v>127116</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C58" t="s">
-        <v>60</v>
+        <v>233</v>
       </c>
       <c r="D58" t="s">
-        <v>61</v>
+        <v>234</v>
       </c>
       <c r="E58" t="s">
-        <v>62</v>
+        <v>235</v>
       </c>
       <c r="F58" t="s">
-        <v>44</v>
+        <v>126</v>
       </c>
       <c r="G58" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="H58" t="s">
-        <v>59</v>
+        <v>232</v>
       </c>
       <c r="I58" t="s">
-        <v>59</v>
+        <v>232</v>
       </c>
       <c r="J58" t="s">
         <v>309</v>
       </c>
       <c r="K58" t="s">
-        <v>42</v>
+        <v>168</v>
       </c>
       <c r="L58" t="s">
         <v>310</v>
@@ -6779,72 +6518,72 @@
         <v>262</v>
       </c>
       <c r="N58" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O58" s="1" t="s">
         <v>311</v>
       </c>
       <c r="P58" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q58" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R58" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S58" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T58" s="2" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="X58" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AA58" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AD58" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG58" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="59" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:33">
       <c r="A59">
         <v>125830</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C59" t="s">
-        <v>147</v>
+        <v>244</v>
       </c>
       <c r="D59" t="s">
-        <v>148</v>
+        <v>245</v>
       </c>
       <c r="E59" t="s">
-        <v>149</v>
+        <v>246</v>
       </c>
       <c r="F59" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="G59" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="H59" t="s">
-        <v>59</v>
+        <v>232</v>
       </c>
       <c r="I59" t="s">
-        <v>59</v>
+        <v>232</v>
       </c>
       <c r="J59" t="s">
         <v>309</v>
       </c>
       <c r="K59" t="s">
-        <v>42</v>
+        <v>168</v>
       </c>
       <c r="L59" t="s">
         <v>310</v>
@@ -6853,72 +6592,72 @@
         <v>262</v>
       </c>
       <c r="N59" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O59" s="1" t="s">
         <v>312</v>
       </c>
       <c r="P59" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q59" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R59" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S59" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T59" s="2" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="X59" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AA59" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AD59" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG59" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="60" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:33">
       <c r="A60">
         <v>120499</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C60" t="s">
-        <v>160</v>
+        <v>250</v>
       </c>
       <c r="D60" t="s">
-        <v>161</v>
+        <v>251</v>
       </c>
       <c r="E60" t="s">
-        <v>162</v>
+        <v>252</v>
       </c>
       <c r="F60" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="G60" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="H60" t="s">
-        <v>59</v>
+        <v>232</v>
       </c>
       <c r="I60" t="s">
-        <v>59</v>
+        <v>232</v>
       </c>
       <c r="J60" t="s">
         <v>309</v>
       </c>
       <c r="K60" t="s">
-        <v>42</v>
+        <v>168</v>
       </c>
       <c r="L60" t="s">
         <v>310</v>
@@ -6927,43 +6666,43 @@
         <v>262</v>
       </c>
       <c r="N60" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O60" s="1" t="s">
         <v>313</v>
       </c>
       <c r="P60" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q60" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="R60" t="s">
-        <v>251</v>
+        <v>46</v>
       </c>
       <c r="S60" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="T60" s="2" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="X60" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AA60" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AD60" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AG60" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2:AG60 AD2:AD60 X2:X60 AA2:AA60" xr:uid="{A937C413-DBBA-49B2-8673-0A7B750C31BC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2:AD60 AA2:AA60 X2:X60 AG2:AG60" xr:uid="{A937C413-DBBA-49B2-8673-0A7B750C31BC}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>

--- a/cert-data/FY26-Healthcare-Certification-Courses_2026-05.xlsx
+++ b/cert-data/FY26-Healthcare-Certification-Courses_2026-05.xlsx
@@ -15,7 +15,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="19">
     <font>
       <name val="Aptos Narrow"/>
@@ -514,7 +516,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -538,6 +540,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1787,14 +1790,20 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AB5" s="9" t="n">
+        <v>46162</v>
+      </c>
       <c r="AD5" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE5" s="9" t="n">
+        <v>46174</v>
       </c>
       <c r="AG5" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2038,10 +2047,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AB7" s="7" t="n"/>
+      <c r="AB7" s="7" t="n">
+        <v>46122</v>
+      </c>
       <c r="AD7" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AE7" s="7" t="n"/>
